--- a/results/fptl_dijkstra.xlsx
+++ b/results/fptl_dijkstra.xlsx
@@ -470,28 +470,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0202</v>
+        <v>0.0194999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0175</v>
+        <v>0.0215</v>
       </c>
       <c r="D2" t="n">
         <v>0.08019999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0814</v>
+        <v>0.0856</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4441</v>
+        <v>0.4342</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4373999999999999</v>
+        <v>0.4436</v>
       </c>
       <c r="H2" t="n">
-        <v>45.57190000000001</v>
+        <v>43.7687</v>
       </c>
       <c r="I2" t="n">
-        <v>46.04010000000001</v>
+        <v>44.00490000000001</v>
       </c>
     </row>
     <row r="3">
@@ -502,25 +502,25 @@
         <v>0.0223999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0203999999999999</v>
+        <v>0.0205999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0668</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0617</v>
+        <v>0.0679</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2875999999999999</v>
+        <v>0.2904</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2766</v>
+        <v>0.2624</v>
       </c>
       <c r="H3" t="n">
-        <v>23.5553</v>
+        <v>22.9376</v>
       </c>
       <c r="I3" t="n">
-        <v>23.6342</v>
+        <v>23.0579</v>
       </c>
     </row>
     <row r="4">
@@ -528,28 +528,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0210999999999999</v>
+        <v>0.0209999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0192</v>
+        <v>0.0213999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.057</v>
+        <v>0.0608</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0576999999999999</v>
+        <v>0.0611</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2415999999999999</v>
+        <v>0.2658999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2378</v>
+        <v>0.2557</v>
       </c>
       <c r="H4" t="n">
-        <v>18.0351</v>
+        <v>23.3135</v>
       </c>
       <c r="I4" t="n">
-        <v>17.9913</v>
+        <v>22.849</v>
       </c>
     </row>
     <row r="5">
@@ -557,28 +557,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0249999999999999</v>
+        <v>0.0208999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0211999999999999</v>
+        <v>0.0221</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0612</v>
+        <v>0.0606</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0613</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2191</v>
+        <v>0.2011</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2149</v>
+        <v>0.2145999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>12.9404</v>
+        <v>13.4271</v>
       </c>
       <c r="I5" t="n">
-        <v>12.9746</v>
+        <v>13.1348</v>
       </c>
     </row>
     <row r="6">
@@ -586,28 +586,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0252</v>
+        <v>0.0215</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0252</v>
+        <v>0.0238999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.064</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="E6" t="n">
         <v>0.0618</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2168</v>
+        <v>0.2111</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2041</v>
+        <v>0.2148</v>
       </c>
       <c r="H6" t="n">
-        <v>14.3764</v>
+        <v>14.15</v>
       </c>
       <c r="I6" t="n">
-        <v>14.2286</v>
+        <v>14.0984</v>
       </c>
     </row>
     <row r="7">
@@ -615,28 +615,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0266999999999999</v>
+        <v>0.0241999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0239999999999999</v>
+        <v>0.0233999999999999</v>
       </c>
       <c r="D7" t="n">
+        <v>0.0678</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.0673</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.0663999999999999</v>
-      </c>
       <c r="F7" t="n">
-        <v>0.2015</v>
+        <v>0.2153</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2065</v>
+        <v>0.2251</v>
       </c>
       <c r="H7" t="n">
-        <v>15.2208</v>
+        <v>15.2297</v>
       </c>
       <c r="I7" t="n">
-        <v>14.9038</v>
+        <v>15.1315</v>
       </c>
     </row>
     <row r="8">
@@ -644,28 +644,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0261</v>
+        <v>0.0273</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0277</v>
+        <v>0.0245999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0684</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0653</v>
+        <v>0.0655</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2069</v>
+        <v>0.2085</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2124</v>
+        <v>0.209</v>
       </c>
       <c r="H8" t="n">
-        <v>16.4669</v>
+        <v>16.338</v>
       </c>
       <c r="I8" t="n">
-        <v>16.3794</v>
+        <v>16.1732</v>
       </c>
     </row>
     <row r="9">
@@ -673,28 +673,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0297</v>
+        <v>0.0292</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0276999999999999</v>
+        <v>0.0274</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0704</v>
+        <v>0.0777999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0696</v>
+        <v>0.0711</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2138999999999999</v>
+        <v>0.2133999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2313</v>
+        <v>0.208</v>
       </c>
       <c r="H9" t="n">
-        <v>13.103</v>
+        <v>12.5341</v>
       </c>
       <c r="I9" t="n">
-        <v>12.7778</v>
+        <v>12.6791</v>
       </c>
     </row>
     <row r="10">
@@ -702,28 +702,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0275</v>
+        <v>0.0328</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0278</v>
+        <v>0.0302</v>
       </c>
       <c r="D10" t="n">
-        <v>0.07229999999999991</v>
+        <v>0.0756</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0779</v>
+        <v>0.07039999999999989</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2151</v>
+        <v>0.2195</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2266999999999999</v>
+        <v>0.214</v>
       </c>
       <c r="H10" t="n">
-        <v>13.9933</v>
+        <v>13.3327</v>
       </c>
       <c r="I10" t="n">
-        <v>13.2714</v>
+        <v>13.0975</v>
       </c>
     </row>
     <row r="11">
@@ -731,28 +731,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0306</v>
+        <v>0.0346</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0281</v>
+        <v>0.031</v>
       </c>
       <c r="D11" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.07229999999999991</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0712</v>
+        <v>0.0717</v>
       </c>
       <c r="F11" t="n">
-        <v>0.213</v>
+        <v>0.227</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2263</v>
+        <v>0.2237</v>
       </c>
       <c r="H11" t="n">
-        <v>13.9536</v>
+        <v>13.3264</v>
       </c>
       <c r="I11" t="n">
-        <v>13.474</v>
+        <v>13.1284</v>
       </c>
     </row>
     <row r="12">
@@ -760,28 +760,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0294</v>
+        <v>0.0323</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0305999999999999</v>
+        <v>0.0349</v>
       </c>
       <c r="D12" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0723</v>
+        <v>0.0769</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2299</v>
+        <v>0.2109</v>
       </c>
       <c r="G12" t="n">
-        <v>0.223</v>
+        <v>0.2165</v>
       </c>
       <c r="H12" t="n">
-        <v>14.0499</v>
+        <v>13.4965</v>
       </c>
       <c r="I12" t="n">
-        <v>13.777</v>
+        <v>13.0734</v>
       </c>
     </row>
     <row r="13">
@@ -789,28 +789,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0377</v>
+        <v>0.0417</v>
       </c>
       <c r="C13" t="n">
-        <v>0.046</v>
+        <v>0.0465999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0779999999999999</v>
+        <v>0.07859999999999991</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0769999999999999</v>
+        <v>0.0842999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2255</v>
+        <v>0.2207</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2218</v>
+        <v>0.2345</v>
       </c>
       <c r="H13" t="n">
-        <v>13.8678</v>
+        <v>13.3342</v>
       </c>
       <c r="I13" t="n">
-        <v>14.0466</v>
+        <v>12.9689</v>
       </c>
     </row>
   </sheetData>
@@ -908,28 +908,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9017857142857183</v>
+        <v>0.8705357142857137</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8578431372549062</v>
+        <v>1.043689320388355</v>
       </c>
       <c r="D3" t="n">
-        <v>1.200598802395209</v>
+        <v>1.213313161875945</v>
       </c>
       <c r="E3" t="n">
-        <v>1.319286871961102</v>
+        <v>1.260677466863034</v>
       </c>
       <c r="F3" t="n">
-        <v>1.544158553546593</v>
+        <v>1.495179063360881</v>
       </c>
       <c r="G3" t="n">
-        <v>1.581344902386117</v>
+        <v>1.690548780487805</v>
       </c>
       <c r="H3" t="n">
-        <v>1.934677121497073</v>
+        <v>1.908163888113839</v>
       </c>
       <c r="I3" t="n">
-        <v>1.948028704165997</v>
+        <v>1.908452200764164</v>
       </c>
     </row>
     <row r="4">
@@ -937,28 +937,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9573459715639855</v>
+        <v>0.9285714285714282</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9114583333333335</v>
+        <v>1.004672897196266</v>
       </c>
       <c r="D4" t="n">
-        <v>1.407017543859649</v>
+        <v>1.319078947368421</v>
       </c>
       <c r="E4" t="n">
-        <v>1.410745233968807</v>
+        <v>1.400981996726677</v>
       </c>
       <c r="F4" t="n">
-        <v>1.83816225165563</v>
+        <v>1.632944716058669</v>
       </c>
       <c r="G4" t="n">
-        <v>1.839360807401177</v>
+        <v>1.734845522096207</v>
       </c>
       <c r="H4" t="n">
-        <v>2.526844874716526</v>
+        <v>1.877397216205203</v>
       </c>
       <c r="I4" t="n">
-        <v>2.559020193093329</v>
+        <v>1.925900477044947</v>
       </c>
     </row>
     <row r="5">
@@ -966,28 +966,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8080000000000032</v>
+        <v>0.9330143540669852</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8254716981132115</v>
+        <v>0.9728506787330315</v>
       </c>
       <c r="D5" t="n">
-        <v>1.310457516339869</v>
+        <v>1.323432343234323</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3278955954323</v>
+        <v>1.293051359516616</v>
       </c>
       <c r="F5" t="n">
-        <v>2.026928343222273</v>
+        <v>2.159124813525609</v>
       </c>
       <c r="G5" t="n">
-        <v>2.035365286179618</v>
+        <v>2.067101584342965</v>
       </c>
       <c r="H5" t="n">
-        <v>3.521676300578035</v>
+        <v>3.259728459607808</v>
       </c>
       <c r="I5" t="n">
-        <v>3.548479336549875</v>
+        <v>3.35025276365076</v>
       </c>
     </row>
     <row r="6">
@@ -995,28 +995,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8015873015873015</v>
+        <v>0.9069767441860419</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6944444444444445</v>
+        <v>0.8995815899581626</v>
       </c>
       <c r="D6" t="n">
-        <v>1.253125</v>
+        <v>1.239567233384853</v>
       </c>
       <c r="E6" t="n">
-        <v>1.317152103559871</v>
+        <v>1.385113268608414</v>
       </c>
       <c r="F6" t="n">
-        <v>2.048431734317343</v>
+        <v>2.056845097110374</v>
       </c>
       <c r="G6" t="n">
-        <v>2.143067123958843</v>
+        <v>2.065176908752328</v>
       </c>
       <c r="H6" t="n">
-        <v>3.169910408725412</v>
+        <v>3.093194346289753</v>
       </c>
       <c r="I6" t="n">
-        <v>3.235743502523089</v>
+        <v>3.121269080179311</v>
       </c>
     </row>
     <row r="7">
@@ -1024,28 +1024,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7565543071161076</v>
+        <v>0.8057851239669414</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7291666666666697</v>
+        <v>0.9188034188034226</v>
       </c>
       <c r="D7" t="n">
-        <v>1.191679049034175</v>
+        <v>1.182890855457227</v>
       </c>
       <c r="E7" t="n">
-        <v>1.225903614457833</v>
+        <v>1.271916790490342</v>
       </c>
       <c r="F7" t="n">
-        <v>2.203970223325062</v>
+        <v>2.016720854621458</v>
       </c>
       <c r="G7" t="n">
-        <v>2.118159806295399</v>
+        <v>1.970679697912039</v>
       </c>
       <c r="H7" t="n">
-        <v>2.99405418900452</v>
+        <v>2.873904279138787</v>
       </c>
       <c r="I7" t="n">
-        <v>3.089151759953838</v>
+        <v>2.90816508607871</v>
       </c>
     </row>
     <row r="8">
@@ -1053,28 +1053,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7739463601532566</v>
+        <v>0.7142857142857105</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6317689530685922</v>
+        <v>0.8739837398374019</v>
       </c>
       <c r="D8" t="n">
-        <v>1.172514619883041</v>
+        <v>1.186390532544379</v>
       </c>
       <c r="E8" t="n">
-        <v>1.246554364471669</v>
+        <v>1.306870229007633</v>
       </c>
       <c r="F8" t="n">
-        <v>2.146447559207346</v>
+        <v>2.082494004796163</v>
       </c>
       <c r="G8" t="n">
-        <v>2.059322033898304</v>
+        <v>2.122488038277512</v>
       </c>
       <c r="H8" t="n">
-        <v>2.767485076122403</v>
+        <v>2.678950911984331</v>
       </c>
       <c r="I8" t="n">
-        <v>2.810853877431409</v>
+        <v>2.72085301610071</v>
       </c>
     </row>
     <row r="9">
@@ -1082,28 +1082,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.68013468013468</v>
+        <v>0.6678082191780788</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6317689530685945</v>
+        <v>0.7846715328467152</v>
       </c>
       <c r="D9" t="n">
-        <v>1.139204545454545</v>
+        <v>1.030848329048844</v>
       </c>
       <c r="E9" t="n">
-        <v>1.169540229885057</v>
+        <v>1.20393811533052</v>
       </c>
       <c r="F9" t="n">
-        <v>2.076203833567088</v>
+        <v>2.034676663542644</v>
       </c>
       <c r="G9" t="n">
-        <v>1.891050583657587</v>
+        <v>2.132692307692308</v>
       </c>
       <c r="H9" t="n">
-        <v>3.477974509654278</v>
+        <v>3.49196990609617</v>
       </c>
       <c r="I9" t="n">
-        <v>3.603131994553054</v>
+        <v>3.470664321600114</v>
       </c>
     </row>
     <row r="10">
@@ -1111,28 +1111,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7345454545454545</v>
+        <v>0.5945121951219481</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6294964028776979</v>
+        <v>0.7119205298013244</v>
       </c>
       <c r="D10" t="n">
-        <v>1.109266943291841</v>
+        <v>1.060846560846561</v>
       </c>
       <c r="E10" t="n">
-        <v>1.044929396662388</v>
+        <v>1.215909090909093</v>
       </c>
       <c r="F10" t="n">
-        <v>2.064621106462111</v>
+        <v>1.978132118451025</v>
       </c>
       <c r="G10" t="n">
-        <v>1.929422143802382</v>
+        <v>2.072897196261682</v>
       </c>
       <c r="H10" t="n">
-        <v>3.256694275117378</v>
+        <v>3.282808433400587</v>
       </c>
       <c r="I10" t="n">
-        <v>3.469121569691216</v>
+        <v>3.359793853788891</v>
       </c>
     </row>
     <row r="11">
@@ -1140,28 +1140,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6601307189542484</v>
+        <v>0.5635838150288989</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6227758007117439</v>
+        <v>0.6935483870967741</v>
       </c>
       <c r="D11" t="n">
-        <v>1.063660477453581</v>
+        <v>1.109266943291841</v>
       </c>
       <c r="E11" t="n">
-        <v>1.143258426966292</v>
+        <v>1.193863319386332</v>
       </c>
       <c r="F11" t="n">
-        <v>2.084976525821596</v>
+        <v>1.912775330396476</v>
       </c>
       <c r="G11" t="n">
-        <v>1.932832523199292</v>
+        <v>1.983012963790791</v>
       </c>
       <c r="H11" t="n">
-        <v>3.265960038986355</v>
+        <v>3.284360367391044</v>
       </c>
       <c r="I11" t="n">
-        <v>3.41695858690812</v>
+        <v>3.351885987629872</v>
       </c>
     </row>
     <row r="12">
@@ -1169,28 +1169,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6870748299319728</v>
+        <v>0.6037151702786346</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5718954248366032</v>
+        <v>0.6160458452722063</v>
       </c>
       <c r="D12" t="n">
-        <v>1.025575447570332</v>
+        <v>1.063660477453581</v>
       </c>
       <c r="E12" t="n">
-        <v>1.125864453665284</v>
+        <v>1.113133940182055</v>
       </c>
       <c r="F12" t="n">
-        <v>1.931709438886472</v>
+        <v>2.058795637743006</v>
       </c>
       <c r="G12" t="n">
-        <v>1.961434977578475</v>
+        <v>2.048960739030023</v>
       </c>
       <c r="H12" t="n">
-        <v>3.243574687364323</v>
+        <v>3.242966695069093</v>
       </c>
       <c r="I12" t="n">
-        <v>3.341808811787764</v>
+        <v>3.365987424847401</v>
       </c>
     </row>
     <row r="13">
@@ -1198,28 +1198,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5358090185676393</v>
+        <v>0.4676258992805731</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3804347826086957</v>
+        <v>0.4613733905579409</v>
       </c>
       <c r="D13" t="n">
-        <v>1.028205128205129</v>
+        <v>1.020356234096693</v>
       </c>
       <c r="E13" t="n">
-        <v>1.057142857142858</v>
+        <v>1.015421115065244</v>
       </c>
       <c r="F13" t="n">
-        <v>1.96940133037694</v>
+        <v>1.967376529225192</v>
       </c>
       <c r="G13" t="n">
-        <v>1.972046889089269</v>
+        <v>1.891684434968017</v>
       </c>
       <c r="H13" t="n">
-        <v>3.286166515236736</v>
+        <v>3.282439141455806</v>
       </c>
       <c r="I13" t="n">
-        <v>3.277668617316646</v>
+        <v>3.393109670056829</v>
       </c>
     </row>
   </sheetData>
@@ -1317,28 +1317,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4508928571428591</v>
+        <v>0.4352678571428569</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4289215686274531</v>
+        <v>0.5218446601941773</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6002994011976047</v>
+        <v>0.6066565809379727</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6596434359805511</v>
+        <v>0.6303387334315169</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7720792767732965</v>
+        <v>0.7475895316804407</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7906724511930584</v>
+        <v>0.8452743902439024</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9673385607485367</v>
+        <v>0.9540819440569197</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9740143520829985</v>
+        <v>0.9542261003820818</v>
       </c>
     </row>
     <row r="4">
@@ -1346,28 +1346,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3191153238546618</v>
+        <v>0.3095238095238094</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3038194444444445</v>
+        <v>0.3348909657320888</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4690058479532164</v>
+        <v>0.4396929824561404</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4702484113229355</v>
+        <v>0.4669939989088925</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6127207505518767</v>
+        <v>0.5443149053528897</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6131202691337256</v>
+        <v>0.5782818406987356</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8422816249055085</v>
+        <v>0.625799072068401</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8530067310311096</v>
+        <v>0.6419668256816492</v>
       </c>
     </row>
     <row r="5">
@@ -1375,28 +1375,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2020000000000008</v>
+        <v>0.2332535885167463</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2063679245283029</v>
+        <v>0.2432126696832579</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3276143790849673</v>
+        <v>0.3308580858085808</v>
       </c>
       <c r="E5" t="n">
-        <v>0.331973898858075</v>
+        <v>0.3232628398791541</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5067320858055683</v>
+        <v>0.5397812033814022</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5088413215449045</v>
+        <v>0.5167753960857412</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8804190751445088</v>
+        <v>0.8149321149019521</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8871198341374688</v>
+        <v>0.8375631909126899</v>
       </c>
     </row>
     <row r="6">
@@ -1404,28 +1404,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1603174603174603</v>
+        <v>0.1813953488372084</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.1799163179916325</v>
       </c>
       <c r="D6" t="n">
-        <v>0.250625</v>
+        <v>0.2479134466769706</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2634304207119741</v>
+        <v>0.2770226537216828</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4096863468634687</v>
+        <v>0.4113690194220748</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4286134247917686</v>
+        <v>0.4130353817504656</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6339820817450823</v>
+        <v>0.6186388692579505</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6471487005046177</v>
+        <v>0.6242538160358622</v>
       </c>
     </row>
     <row r="7">
@@ -1433,28 +1433,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1260923845193513</v>
+        <v>0.1342975206611569</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1215277777777783</v>
+        <v>0.1531339031339038</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1986131748390292</v>
+        <v>0.1971484759095379</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2043172690763055</v>
+        <v>0.2119861317483903</v>
       </c>
       <c r="F7" t="n">
-        <v>0.367328370554177</v>
+        <v>0.3361201424369097</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3530266343825665</v>
+        <v>0.3284466163186732</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4990090315007534</v>
+        <v>0.4789840465231312</v>
       </c>
       <c r="I7" t="n">
-        <v>0.514858626658973</v>
+        <v>0.4846941810131184</v>
       </c>
     </row>
     <row r="8">
@@ -1462,28 +1462,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1105637657361795</v>
+        <v>0.1020408163265301</v>
       </c>
       <c r="C8" t="n">
-        <v>0.09025270758122746</v>
+        <v>0.1248548199767717</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1675020885547201</v>
+        <v>0.1694843617920541</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1780791949245242</v>
+        <v>0.1866957470010905</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3066353656010495</v>
+        <v>0.297499143542309</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2941888619854721</v>
+        <v>0.3032125768967874</v>
       </c>
       <c r="H8" t="n">
-        <v>0.395355010874629</v>
+        <v>0.3827072731406188</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4015505539187726</v>
+        <v>0.3886932880143871</v>
       </c>
     </row>
     <row r="9">
@@ -1491,28 +1491,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.085016835016835</v>
+        <v>0.08347602739725984</v>
       </c>
       <c r="C9" t="n">
-        <v>0.07897111913357431</v>
+        <v>0.0980839416058394</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1424005681818181</v>
+        <v>0.1288560411311055</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1461925287356322</v>
+        <v>0.1504922644163151</v>
       </c>
       <c r="F9" t="n">
-        <v>0.259525479195886</v>
+        <v>0.2543345829428305</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2363813229571984</v>
+        <v>0.2665865384615385</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4347468137067848</v>
+        <v>0.4364962382620212</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4503914993191317</v>
+        <v>0.4338330402000142</v>
       </c>
     </row>
     <row r="10">
@@ -1520,28 +1520,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.08161616161616161</v>
+        <v>0.06605691056910534</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06994404476418865</v>
+        <v>0.07910228108903604</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1232518825879823</v>
+        <v>0.1178718400940623</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1161032662958209</v>
+        <v>0.1351010101010103</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2294023451624567</v>
+        <v>0.2197924576056695</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2143802382002647</v>
+        <v>0.2303219106957425</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3618549194574865</v>
+        <v>0.3647564926000652</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3854579521879129</v>
+        <v>0.3733104281987657</v>
       </c>
     </row>
     <row r="11">
@@ -1549,28 +1549,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.06601307189542484</v>
+        <v>0.05635838150288989</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06227758007117438</v>
+        <v>0.06935483870967742</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1063660477453581</v>
+        <v>0.1109266943291841</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1143258426966292</v>
+        <v>0.1193863319386332</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2084976525821596</v>
+        <v>0.1912775330396476</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1932832523199292</v>
+        <v>0.1983012963790791</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3265960038986355</v>
+        <v>0.3284360367391044</v>
       </c>
       <c r="I11" t="n">
-        <v>0.341695858690812</v>
+        <v>0.3351885987629872</v>
       </c>
     </row>
     <row r="12">
@@ -1578,28 +1578,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.06246134817563389</v>
+        <v>0.05488319729805769</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05199049316696392</v>
+        <v>0.05600416775201875</v>
       </c>
       <c r="D12" t="n">
-        <v>0.09323413159730293</v>
+        <v>0.09669640704123462</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1023513139695712</v>
+        <v>0.101193994562005</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1756099489896793</v>
+        <v>0.1871632397948187</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1783122706889523</v>
+        <v>0.1862691580936384</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2948704261240294</v>
+        <v>0.2948151540971902</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3038008010716149</v>
+        <v>0.3059988568043092</v>
       </c>
     </row>
     <row r="13">
@@ -1607,28 +1607,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.04465075154730327</v>
+        <v>0.03896882494004776</v>
       </c>
       <c r="C13" t="n">
-        <v>0.03170289855072464</v>
+        <v>0.03844778254649508</v>
       </c>
       <c r="D13" t="n">
-        <v>0.08568376068376078</v>
+        <v>0.08502968617472444</v>
       </c>
       <c r="E13" t="n">
-        <v>0.08809523809523821</v>
+        <v>0.08461842625543703</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1641167775314117</v>
+        <v>0.1639480441020994</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1643372407574391</v>
+        <v>0.1576403695806681</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2738472096030613</v>
+        <v>0.2735365951213172</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2731390514430539</v>
+        <v>0.2827591391714024</v>
       </c>
     </row>
   </sheetData>
